--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,1072 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131772648</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91825</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6913619</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131772640</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91849</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564053</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6913635</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131772644</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80270</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563760</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6913797</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131772649</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91792</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563744</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6913597</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131772639</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80366</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564080</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6913612</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131772647</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83107</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563821</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6913646</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131772643</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92552</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563804</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6913800</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131772645</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563709</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6913779</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131772641</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97148</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564014</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6913642</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131772646</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5198</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartåstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563830</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6913655</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772647</v>
+        <v>131772643</v>
       </c>
       <c r="B9" t="n">
-        <v>83107</v>
+        <v>92552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563821</v>
+        <v>563804</v>
       </c>
       <c r="R9" t="n">
-        <v>6913646</v>
+        <v>6913800</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,32 +1539,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131772643</v>
+        <v>131772647</v>
       </c>
       <c r="B10" t="n">
-        <v>92552</v>
+        <v>83107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563804</v>
+        <v>563821</v>
       </c>
       <c r="R10" t="n">
-        <v>6913800</v>
+        <v>6913646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,32 +1646,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772645</v>
+        <v>131772641</v>
       </c>
       <c r="B11" t="n">
-        <v>91829</v>
+        <v>97148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563709</v>
+        <v>564014</v>
       </c>
       <c r="R11" t="n">
-        <v>6913779</v>
+        <v>6913642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772641</v>
+        <v>131772645</v>
       </c>
       <c r="B12" t="n">
-        <v>97148</v>
+        <v>91829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564014</v>
+        <v>563709</v>
       </c>
       <c r="R12" t="n">
-        <v>6913642</v>
+        <v>6913779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>131772648</v>
       </c>
       <c r="B4" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>131772640</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>131772644</v>
       </c>
       <c r="B6" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131772649</v>
       </c>
       <c r="B7" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131772639</v>
       </c>
       <c r="B8" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131772643</v>
       </c>
       <c r="B9" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131772647</v>
       </c>
       <c r="B10" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131772641</v>
       </c>
       <c r="B11" t="n">
-        <v>97148</v>
+        <v>97151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>131772645</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -1008,30 +1008,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131772640</v>
+        <v>131772644</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>80273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564053</v>
+        <v>563760</v>
       </c>
       <c r="R5" t="n">
-        <v>6913635</v>
+        <v>6913797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,34 +1115,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131772644</v>
+        <v>131772640</v>
       </c>
       <c r="B6" t="n">
-        <v>80273</v>
+        <v>91852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563760</v>
+        <v>564053</v>
       </c>
       <c r="R6" t="n">
-        <v>6913797</v>
+        <v>6913635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772643</v>
+        <v>131772647</v>
       </c>
       <c r="B9" t="n">
-        <v>92555</v>
+        <v>83110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563804</v>
+        <v>563821</v>
       </c>
       <c r="R9" t="n">
-        <v>6913800</v>
+        <v>6913646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,32 +1539,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131772647</v>
+        <v>131772643</v>
       </c>
       <c r="B10" t="n">
-        <v>83110</v>
+        <v>92555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563821</v>
+        <v>563804</v>
       </c>
       <c r="R10" t="n">
-        <v>6913646</v>
+        <v>6913800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>131772648</v>
       </c>
       <c r="B4" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>131772644</v>
       </c>
       <c r="B5" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>131772640</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131772649</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131772639</v>
       </c>
       <c r="B8" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131772647</v>
       </c>
       <c r="B9" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131772643</v>
       </c>
       <c r="B10" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,32 +1646,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772641</v>
+        <v>131772645</v>
       </c>
       <c r="B11" t="n">
-        <v>97151</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564014</v>
+        <v>563709</v>
       </c>
       <c r="R11" t="n">
-        <v>6913642</v>
+        <v>6913779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772645</v>
+        <v>131772641</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>97157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563709</v>
+        <v>564014</v>
       </c>
       <c r="R12" t="n">
-        <v>6913779</v>
+        <v>6913642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>131772648</v>
       </c>
       <c r="B4" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,34 +1008,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131772644</v>
+        <v>131772640</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>91912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563760</v>
+        <v>564053</v>
       </c>
       <c r="R5" t="n">
-        <v>6913797</v>
+        <v>6913635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,30 +1111,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131772640</v>
+        <v>131772644</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564053</v>
+        <v>563760</v>
       </c>
       <c r="R6" t="n">
-        <v>6913635</v>
+        <v>6913797</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
         <v>131772649</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131772639</v>
       </c>
       <c r="B8" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131772647</v>
       </c>
       <c r="B9" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131772643</v>
       </c>
       <c r="B10" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131772645</v>
       </c>
       <c r="B11" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>131772641</v>
       </c>
       <c r="B12" t="n">
-        <v>97208</v>
+        <v>97211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772647</v>
+        <v>131772643</v>
       </c>
       <c r="B9" t="n">
-        <v>83163</v>
+        <v>92615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563821</v>
+        <v>563804</v>
       </c>
       <c r="R9" t="n">
-        <v>6913646</v>
+        <v>6913800</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,32 +1539,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131772643</v>
+        <v>131772647</v>
       </c>
       <c r="B10" t="n">
-        <v>92615</v>
+        <v>83163</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563804</v>
+        <v>563821</v>
       </c>
       <c r="R10" t="n">
-        <v>6913800</v>
+        <v>6913646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8324-2025 artfynd.xlsx
+++ b/artfynd/A 8324-2025 artfynd.xlsx
@@ -1646,32 +1646,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772645</v>
+        <v>131772641</v>
       </c>
       <c r="B11" t="n">
-        <v>91892</v>
+        <v>97211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563709</v>
+        <v>564014</v>
       </c>
       <c r="R11" t="n">
-        <v>6913779</v>
+        <v>6913642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772641</v>
+        <v>131772645</v>
       </c>
       <c r="B12" t="n">
-        <v>97211</v>
+        <v>91892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564014</v>
+        <v>563709</v>
       </c>
       <c r="R12" t="n">
-        <v>6913642</v>
+        <v>6913779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
